--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815705</v>
       </c>
       <c r="B3" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>122815705</v>
       </c>
       <c r="B3" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815705</v>
       </c>
       <c r="B3" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815705</v>
       </c>
       <c r="B3" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122777285</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
+        <v>78508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>122815705</v>
       </c>
       <c r="B3" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,220 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128297033</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>788</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477453</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6593522</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128297003</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92676</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>477445</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6593546</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,7 +890,7 @@
         <v>128297033</v>
       </c>
       <c r="B4" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128297003</v>
       </c>
       <c r="B5" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,6 +1098,113 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128483407</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477439</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6593476</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128297033</v>
       </c>
       <c r="B4" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128297003</v>
       </c>
       <c r="B5" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128297033</v>
       </c>
       <c r="B4" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128297003</v>
       </c>
       <c r="B5" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128297033</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128297003</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128297033</v>
       </c>
       <c r="B4" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128297003</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,6 +1205,113 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128818315</v>
+      </c>
+      <c r="B7" t="n">
+        <v>75196</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>308</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477527</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6593539</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128297033</v>
       </c>
       <c r="B4" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128297003</v>
       </c>
       <c r="B5" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>128818315</v>
       </c>
       <c r="B7" t="n">
-        <v>75196</v>
+        <v>75197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128297033</v>
       </c>
       <c r="B4" t="n">
-        <v>92786</v>
+        <v>92796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>128297003</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>128818315</v>
       </c>
       <c r="B7" t="n">
-        <v>75197</v>
+        <v>75201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>128483407</v>
       </c>
       <c r="B6" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>128818315</v>
       </c>
       <c r="B7" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1211,7 +1211,7 @@
         <v>128818315</v>
       </c>
       <c r="B7" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1211,7 +1211,7 @@
         <v>128818315</v>
       </c>
       <c r="B7" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1211,7 +1211,7 @@
         <v>128818315</v>
       </c>
       <c r="B7" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57379-2020 artfynd.xlsx
+++ b/artfynd/A 57379-2020 artfynd.xlsx
@@ -1211,7 +1211,7 @@
         <v>128818315</v>
       </c>
       <c r="B7" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
